--- a/histograms/histogram_Valence_electrons.xlsx
+++ b/histograms/histogram_Valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>4.95</v>
       </c>
       <c r="B2" t="n">
-        <v>1989</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>6.85</v>
       </c>
       <c r="B3" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>8.75</v>
       </c>
       <c r="B4" t="n">
-        <v>2218</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>10.65</v>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>12.55</v>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>14.45</v>
       </c>
       <c r="B7" t="n">
-        <v>2606</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>16.35</v>
       </c>
       <c r="B8" t="n">
-        <v>323</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>18.25</v>
       </c>
       <c r="B9" t="n">
-        <v>1450</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>20.15</v>
       </c>
       <c r="B10" t="n">
-        <v>11857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>22.05</v>
       </c>
       <c r="B11" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>23.95</v>
       </c>
       <c r="B12" t="n">
-        <v>1290</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>25.85</v>
       </c>
       <c r="B13" t="n">
-        <v>1104</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>27.75</v>
       </c>
       <c r="B14" t="n">
-        <v>338</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>29.65</v>
       </c>
       <c r="B15" t="n">
-        <v>345</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -565,7 +565,7 @@
         <v>33.45</v>
       </c>
       <c r="B17" t="n">
-        <v>1030</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -597,7 +597,7 @@
         <v>41.05</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
